--- a/04_DESIGN_TABLES/DesignTable_2705.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2705.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,6 +499,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -544,12 +549,17 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>Air-Way s73 only (double-pass 21 rows)</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L24@DRIVE=1.84~1.840; C5HEX@HEX=0.69~0.688; D@BORE=0.17~0.172</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -607,12 +617,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>Air-Way s73 only (double-pass 21 rows)</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L24@DRIVE=1.84~1.840; C5HEX@HEX=0.69~0.688; D@BORE=0.17~0.172</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -885,13 +900,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="C9" t="n">
         <v>1.28</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="E9" t="n">
         <v>0.3</v>
@@ -932,12 +947,17 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1046 = 2.220 (table had 2.18) | Brennan TFA TFA-p008-t04: agrees on L24@DRIVE, D@BORE | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): C5HEX@HEX 1 -&gt; 0.875</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2705-06-06</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1094,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="C12" t="n">
         <v>1.44</v>
@@ -1121,12 +1141,17 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1047 = 2.390 (table had 2.34) | Brennan TFA TFA-p008-t04: agrees on L24@DRIVE, D@BORE</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2705-06-08</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1225,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="C14" t="n">
         <v>1.44</v>
@@ -1247,12 +1272,17 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1048 = 2.610 (table had 2.58) | Brennan TFA TFA-p008-t04: agrees on L24@DRIVE, D@BORE</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2705-08-08</t>
         </is>
       </c>
     </row>
@@ -1931,6 +1961,74 @@
       <c r="P26" t="inlineStr">
         <is>
           <t>2705-LN-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2705-06-04</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2705-06-04</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>3/8-18 (A NPTF) x 7/16-20 (B UN/UNF-2A)</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; L24 / hex / bore: OMi WebsitePartsInfo2026 Items (= Brennan TFA p.8, one source); I1 = Air-Way -04 bulkhead length (A8); tap drill = Air-Way per size (A1); JIC end MS33656J</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; L24 / hex / bore from OMi Items (= Brennan TFA p.8), I1 = Air-Way per size (A8)</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2705-06-04</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>OMI</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_2705.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2705.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
         <v>1.2</v>
@@ -690,7 +690,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1043 Overall Length = 2.080 (table had 2) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1043 Overall Length = 2.080 (table had 2) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L24@DRIVE: Air-Way 2 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.08) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L24@DRIVE OMi/Brennan 2.08 -&gt; Air-Way 2</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -711,7 +716,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
         <v>1.2</v>
@@ -753,7 +758,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1057 Overall Length = 2.080 (table had 2) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1057 Overall Length = 2.080 (table had 2) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L24@DRIVE: Air-Way 2 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.08) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L24@DRIVE OMi/Brennan 2.08 -&gt; Air-Way 2</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -774,7 +784,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="C7" t="n">
         <v>1.28</v>
@@ -816,7 +826,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1044 Overall Length = 2.170 (table had 2.08) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1044 Overall Length = 2.170 (table had 2.08) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L24@DRIVE: Air-Way 2.08 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.17) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L24@DRIVE OMi/Brennan 2.17 -&gt; Air-Way 2.08</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -837,7 +852,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="C8" t="n">
         <v>1.28</v>
@@ -879,7 +894,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1058 Overall Length = 2.170 (table had 2.08) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1058 Overall Length = 2.170 (table had 2.08) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L24@DRIVE: Air-Way 2.08 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.17) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L24@DRIVE OMi/Brennan 2.17 -&gt; Air-Way 2.08</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -900,13 +920,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="C9" t="n">
         <v>1.28</v>
       </c>
       <c r="D9" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0.3</v>
@@ -942,12 +962,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows)</t>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: Air-Way 2.18 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.22) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C5HEX@HEX: Air-Way 1 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.875) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1046 = 2.220 (table had 2.18) | Brennan TFA TFA-p008-t04: agrees on L24@DRIVE, D@BORE | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): C5HEX@HEX 1 -&gt; 0.875</t>
+          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1046 = 2.220 (table had 2.18) | Brennan TFA TFA-p008-t04: agrees on L24@DRIVE, D@BORE | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): C5HEX@HEX 1 -&gt; 0.875 | 2026-10-20 Air-Way first: L24@DRIVE OMi/Brennan 2.22 -&gt; Air-Way 2.18 | 2026-10-20 Air-Way first: C5HEX@HEX OMi/Brennan 0.875 -&gt; Air-Way 1</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -968,13 +988,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="C10" t="n">
         <v>1.28</v>
       </c>
       <c r="D10" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0.3</v>
@@ -1010,7 +1030,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1060 Overall Length = 2.220 (table had 2.18); C5HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1060 Hex Flat = 0.875 (table had 1) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1060 Overall Length = 2.220 (table had 2.18); C5HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1060 Hex Flat = 0.875 (table had 1) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L24@DRIVE: Air-Way 2.18 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.22) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C5HEX@HEX: Air-Way 1 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.875) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L24@DRIVE OMi/Brennan 2.22 -&gt; Air-Way 2.18 | 2026-10-20 Air-Way first: C5HEX@HEX OMi/Brennan 0.875 -&gt; Air-Way 1</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1094,7 +1119,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="C12" t="n">
         <v>1.44</v>
@@ -1136,12 +1161,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows)</t>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: Air-Way 2.34 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.39) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1047 = 2.390 (table had 2.34) | Brennan TFA TFA-p008-t04: agrees on L24@DRIVE, D@BORE</t>
+          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1047 = 2.390 (table had 2.34) | Brennan TFA TFA-p008-t04: agrees on L24@DRIVE, D@BORE | 2026-10-20 Air-Way first: L24@DRIVE OMi/Brennan 2.39 -&gt; Air-Way 2.34</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1225,7 +1250,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="C14" t="n">
         <v>1.44</v>
@@ -1267,12 +1292,12 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows)</t>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: Air-Way 2.58 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.61) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1048 = 2.610 (table had 2.58) | Brennan TFA TFA-p008-t04: agrees on L24@DRIVE, D@BORE</t>
+          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1048 = 2.610 (table had 2.58) | Brennan TFA TFA-p008-t04: agrees on L24@DRIVE, D@BORE | 2026-10-20 Air-Way first: L24@DRIVE OMi/Brennan 2.61 -&gt; Air-Way 2.58</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1293,7 +1318,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="C15" t="n">
         <v>1.44</v>
@@ -1335,7 +1360,12 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1062 Overall Length = 2.610 (table had 2.58) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1062 Overall Length = 2.610 (table had 2.58) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L24@DRIVE: Air-Way 2.58 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.61) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L24@DRIVE OMi/Brennan 2.61 -&gt; Air-Way 2.58</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1356,7 +1386,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.84</v>
+        <v>2.66</v>
       </c>
       <c r="C16" t="n">
         <v>1.58</v>
@@ -1398,7 +1428,12 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1049 Overall Length = 2.840 (table had 2.66) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1049 Overall Length = 2.840 (table had 2.66) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L24@DRIVE: Air-Way 2.66 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.84) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L24@DRIVE OMi/Brennan 2.84 -&gt; Air-Way 2.66</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1419,7 +1454,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.84</v>
+        <v>2.66</v>
       </c>
       <c r="C17" t="n">
         <v>1.58</v>
@@ -1461,7 +1496,12 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1063 Overall Length = 2.840 (table had 2.66) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1063 Overall Length = 2.840 (table had 2.66) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L24@DRIVE: Air-Way 2.66 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.84) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L24@DRIVE OMi/Brennan 2.84 -&gt; Air-Way 2.66</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1482,7 +1522,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="C18" t="n">
         <v>1.75</v>
@@ -1524,7 +1564,12 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1050 Overall Length = 2.990 (table had 2.92) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1050 Overall Length = 2.990 (table had 2.92) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L24@DRIVE: Air-Way 2.92 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.99) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L24@DRIVE OMi/Brennan 2.99 -&gt; Air-Way 2.92</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1545,7 +1590,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="C19" t="n">
         <v>1.75</v>
@@ -1587,7 +1632,12 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1064 Overall Length = 2.990 (table had 2.92) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1064 Overall Length = 2.990 (table had 2.92) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L24@DRIVE: Air-Way 2.92 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.99) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L24@DRIVE OMi/Brennan 2.99 -&gt; Air-Way 2.92</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1608,7 +1658,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.23</v>
+        <v>3.09</v>
       </c>
       <c r="C20" t="n">
         <v>1.75</v>
@@ -1650,7 +1700,12 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1052 Overall Length = 3.230 (table had 3.09) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1052 Overall Length = 3.230 (table had 3.09) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L24@DRIVE: Air-Way 3.09 (raw 07_RAW_EXTRACTS; OMi file / Brennan 3.23) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L24@DRIVE OMi/Brennan 3.23 -&gt; Air-Way 3.09</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1671,7 +1726,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.23</v>
+        <v>3.09</v>
       </c>
       <c r="C21" t="n">
         <v>1.75</v>
@@ -1713,7 +1768,12 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1066 Overall Length = 3.230 (table had 3.09) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1066 Overall Length = 3.230 (table had 3.09) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L24@DRIVE: Air-Way 3.09 (raw 07_RAW_EXTRACTS; OMi file / Brennan 3.23) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L24@DRIVE OMi/Brennan 3.23 -&gt; Air-Way 3.09</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_2705.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2705.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1993,24 +1993,55 @@
           <t>2705-LN-06-04</t>
         </is>
       </c>
+      <c r="B26" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>2705-LN-06-04</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>3/8-18 (A NPTF) x 7/16-20 (B UN/UNF-2A)</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): L24 / hex / D = OMi WebsitePartsInfo2026.xlsx Items row 1059 (own -LN row; = the plain 2705-06-04); I1 1.20 = Air-Way -04 bulkhead (A8); tap drill 0.57 = Air-Way -06 (A1); -LN modelled as the plain part, no locknut (A10); thread majors from the end library</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-20 batch-19 stage A_answered (not shipped): filled from OMi Items row 1059 + A8 I1 / A1 tap drill / A10 (-LN = the plain part, values equal the plain 2705-06-04 row)</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2021,6 +2052,11 @@
       <c r="P26" t="inlineStr">
         <is>
           <t>2705-LN-06-04</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>OMI</t>
         </is>
       </c>
     </row>
